--- a/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -614,7 +614,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -630,13 +633,25 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement</t>
-  </si>
-  <si>
-    <t>bodyMeasurement</t>
-  </si>
-  <si>
-    <t>Observation.category:bodyMeasurement.id</t>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>検査の第1カテゴリはJP_SimpleObservationCategory_VSから値を指定する。</t>
+  </si>
+  <si>
+    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+  </si>
+  <si>
+    <t>Observation.category:first.id</t>
   </si>
   <si>
     <t>Observation.category.id</t>
@@ -658,7 +673,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement.extension</t>
+    <t>Observation.category:first.extension</t>
   </si>
   <si>
     <t>Observation.category.extension</t>
@@ -677,7 +692,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement.coding</t>
+    <t>Observation.category:first.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
@@ -708,19 +723,19 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement.coding.id</t>
+    <t>Observation.category:first.coding.id</t>
   </si>
   <si>
     <t>Observation.category.coding.id</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement.coding.extension</t>
+    <t>Observation.category:first.coding.extension</t>
   </si>
   <si>
     <t>Observation.category.coding.extension</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement.coding.system</t>
+    <t>Observation.category:first.coding.system</t>
   </si>
   <si>
     <t>Observation.category.coding.system</t>
@@ -750,7 +765,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement.coding.version</t>
+    <t>Observation.category:first.coding.version</t>
   </si>
   <si>
     <t>Observation.category.coding.version</t>
@@ -774,7 +789,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement.coding.code</t>
+    <t>Observation.category:first.coding.code</t>
   </si>
   <si>
     <t>Observation.category.coding.code</t>
@@ -801,7 +816,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement.coding.display</t>
+    <t>Observation.category:first.coding.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -825,7 +840,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement.coding.userSelected</t>
+    <t>Observation.category:first.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -856,7 +871,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurement.text</t>
+    <t>Observation.category:first.text</t>
   </si>
   <si>
     <t>Observation.category.text</t>
@@ -883,10 +898,10 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurementCategory</t>
-  </si>
-  <si>
-    <t>bodyMeasurementCategory</t>
+    <t>Observation.category:second</t>
+  </si>
+  <si>
+    <t>second</t>
   </si>
   <si>
     <t>MEDISの看護実践用語標準マスター＜看護観察編＞の大分類１．バイタルサイン・基本情報、中分類2．身体計測の「焦点」</t>
@@ -895,40 +910,40 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCategory_VS</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurementCategory.id</t>
-  </si>
-  <si>
-    <t>Observation.category:bodyMeasurementCategory.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:bodyMeasurementCategory.coding</t>
-  </si>
-  <si>
-    <t>Observation.category:bodyMeasurementCategory.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:bodyMeasurementCategory.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:bodyMeasurementCategory.coding.system</t>
+    <t>Observation.category:second.id</t>
+  </si>
+  <si>
+    <t>Observation.category:second.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.system</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationBodyMeasurementCategory_CS</t>
   </si>
   <si>
-    <t>Observation.category:bodyMeasurementCategory.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category:bodyMeasurementCategory.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.category:bodyMeasurementCategory.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.category:bodyMeasurementCategory.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category:bodyMeasurementCategory.text</t>
+    <t>Observation.category:second.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category:second.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1258,10 +1273,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1303,7 +1315,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>
@@ -1366,7 +1378,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1967,9 +1979,9 @@
   <dimension ref="A1:AP75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="66.28515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="26.578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3767,22 +3779,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3809,10 +3823,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3820,13 +3834,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -3836,7 +3850,7 @@
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -3851,13 +3865,13 @@
         <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>191</v>
@@ -3889,7 +3903,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3931,10 +3945,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -3942,10 +3956,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3968,13 +3982,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4025,7 +4039,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4049,7 +4063,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4060,10 +4074,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4092,7 +4106,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4133,19 +4147,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4169,7 +4183,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4180,10 +4194,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4206,19 +4220,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4267,7 +4281,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4288,10 +4302,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4302,10 +4316,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4328,13 +4342,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4385,7 +4399,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4409,7 +4423,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4420,10 +4434,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4452,7 +4466,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4493,19 +4507,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4529,7 +4543,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4540,10 +4554,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4569,23 +4583,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4627,7 +4641,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4648,10 +4662,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4662,10 +4676,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4688,16 +4702,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4747,7 +4761,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4768,10 +4782,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4782,10 +4796,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4811,21 +4825,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4867,7 +4881,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4888,10 +4902,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4902,10 +4916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4928,17 +4942,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4987,7 +5001,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5008,10 +5022,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5022,10 +5036,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5048,19 +5062,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5109,7 +5123,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5130,10 +5144,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5144,10 +5158,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5170,19 +5184,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5231,7 +5245,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5252,10 +5266,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5266,13 +5280,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5303,7 +5317,7 @@
         <v>189</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>191</v>
@@ -5335,7 +5349,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5377,10 +5391,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5388,10 +5402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5414,13 +5428,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5471,7 +5485,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5495,7 +5509,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5506,10 +5520,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5538,7 +5552,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5579,19 +5593,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5615,7 +5629,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5626,10 +5640,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5652,19 +5666,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5713,7 +5727,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5734,10 +5748,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5748,10 +5762,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5774,13 +5788,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5831,7 +5845,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5855,7 +5869,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5866,10 +5880,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5898,7 +5912,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -5939,19 +5953,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5975,7 +5989,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -5986,10 +6000,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6015,16 +6029,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6034,7 +6048,7 @@
         <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>83</v>
@@ -6073,7 +6087,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6094,10 +6108,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6108,10 +6122,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6134,16 +6148,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6193,7 +6207,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6214,10 +6228,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6228,10 +6242,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6257,14 +6271,14 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6313,7 +6327,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6334,10 +6348,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6348,10 +6362,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6374,17 +6388,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6433,7 +6447,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6454,10 +6468,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6468,10 +6482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6494,19 +6508,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6555,7 +6569,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6576,10 +6590,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6590,10 +6604,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6616,19 +6630,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6677,7 +6691,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6698,10 +6712,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6712,14 +6726,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6741,16 +6755,16 @@
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6779,25 +6793,25 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -6812,30 +6826,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6858,19 +6872,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6919,7 +6933,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6934,19 +6948,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -6954,10 +6968,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6980,16 +6994,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7039,7 +7053,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7060,13 +7074,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7074,14 +7088,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7100,19 +7114,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7161,7 +7175,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7176,19 +7190,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7196,14 +7210,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7222,19 +7236,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7283,7 +7297,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7298,19 +7312,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7318,10 +7332,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7344,16 +7358,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7403,7 +7417,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7424,13 +7438,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7438,10 +7452,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7464,19 +7478,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7525,7 +7539,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7540,19 +7554,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7560,10 +7574,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7586,19 +7600,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7647,7 +7661,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7656,7 +7670,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7665,27 +7679,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7711,16 +7725,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7745,31 +7759,31 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7778,7 +7792,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7793,7 +7807,7 @@
         <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7804,14 +7818,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7833,16 +7847,16 @@
         <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7867,31 +7881,31 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7909,27 +7923,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7952,19 +7966,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8013,7 +8027,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8034,10 +8048,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8048,10 +8062,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8077,13 +8091,13 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8109,31 +8123,29 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8151,27 +8163,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8197,16 +8209,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8231,31 +8243,31 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8276,10 +8288,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8290,10 +8302,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8316,16 +8328,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8375,7 +8387,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8393,27 +8405,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8436,16 +8448,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8495,7 +8507,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8513,27 +8525,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8556,19 +8568,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8617,7 +8629,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8629,7 +8641,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8638,10 +8650,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8652,10 +8664,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8678,13 +8690,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8735,7 +8747,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8759,7 +8771,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8770,10 +8782,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8802,7 +8814,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8855,7 +8867,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8879,7 +8891,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8890,14 +8902,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8919,10 +8931,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -8977,7 +8989,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9012,10 +9024,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9038,13 +9050,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9095,7 +9107,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9104,7 +9116,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9116,10 +9128,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9130,10 +9142,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9156,13 +9168,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9213,7 +9225,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9222,7 +9234,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9234,10 +9246,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9248,10 +9260,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9277,16 +9289,16 @@
         <v>188</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9314,10 +9326,10 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9335,7 +9347,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9353,13 +9365,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9370,10 +9382,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9399,16 +9411,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9433,13 +9445,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9457,7 +9469,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9475,13 +9487,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9492,10 +9504,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9518,17 +9530,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9577,7 +9589,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9601,7 +9613,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9612,10 +9624,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9638,13 +9650,13 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9695,7 +9707,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9716,10 +9728,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9730,10 +9742,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9756,16 +9768,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9815,7 +9827,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9836,10 +9848,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9850,10 +9862,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9876,16 +9888,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9935,7 +9947,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9956,10 +9968,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9970,10 +9982,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9996,19 +10008,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10057,7 +10069,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10078,10 +10090,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10092,10 +10104,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10118,13 +10130,13 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10175,7 +10187,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10199,7 +10211,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10210,10 +10222,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10242,7 +10254,7 @@
         <v>141</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>143</v>
@@ -10295,7 +10307,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10319,7 +10331,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10330,14 +10342,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10359,10 +10371,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10417,7 +10429,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10452,10 +10464,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10481,16 +10493,16 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10515,31 +10527,31 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10557,16 +10569,16 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -10574,10 +10586,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10600,19 +10612,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10661,7 +10673,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10679,27 +10691,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10725,16 +10737,16 @@
         <v>188</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10759,13 +10771,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10783,7 +10795,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10792,7 +10804,7 @@
         <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>106</v>
@@ -10807,7 +10819,7 @@
         <v>137</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10818,14 +10830,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10847,16 +10859,16 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10881,13 +10893,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10905,7 +10917,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10923,27 +10935,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10969,16 +10981,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11027,7 +11039,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11048,10 +11060,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1189,7 +1189,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1273,7 +1273,10 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1379,7 +1382,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1450,7 +1453,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
@@ -1641,7 +1644,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2003,7 +2006,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="74.08984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -8125,9 +8128,11 @@
       <c r="X51" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="Y51" s="2"/>
+      <c r="Y51" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8163,27 +8168,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8209,16 +8214,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8246,10 +8251,10 @@
         <v>403</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8267,7 +8272,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8288,10 +8293,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8302,10 +8307,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8328,16 +8333,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8387,7 +8392,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8405,27 +8410,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8448,16 +8453,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8507,7 +8512,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8525,27 +8530,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8568,19 +8573,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8629,7 +8634,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8641,7 +8646,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8650,10 +8655,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8664,10 +8669,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8782,10 +8787,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8902,14 +8907,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8931,10 +8936,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -8989,7 +8994,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9024,10 +9029,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9050,13 +9055,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9107,7 +9112,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9116,7 +9121,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9128,10 +9133,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9142,10 +9147,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9168,13 +9173,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9225,7 +9230,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9234,7 +9239,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9246,10 +9251,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9260,10 +9265,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9289,16 +9294,16 @@
         <v>188</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9326,10 +9331,10 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9347,7 +9352,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9365,10 +9370,10 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>391</v>
@@ -9382,10 +9387,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9411,16 +9416,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9448,10 +9453,10 @@
         <v>403</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9469,7 +9474,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9487,10 +9492,10 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>391</v>
@@ -9504,10 +9509,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9530,17 +9535,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9589,7 +9594,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9613,7 +9618,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9624,10 +9629,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9653,10 +9658,10 @@
         <v>206</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9707,7 +9712,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9728,10 +9733,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9742,10 +9747,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9768,16 +9773,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9827,7 +9832,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9848,10 +9853,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9862,10 +9867,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9888,16 +9893,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9947,7 +9952,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9968,10 +9973,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9982,10 +9987,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10008,19 +10013,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10069,7 +10074,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10090,10 +10095,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10104,10 +10109,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10222,10 +10227,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10342,14 +10347,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10371,10 +10376,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10429,7 +10434,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10464,10 +10469,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10493,13 +10498,13 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>305</v>
@@ -10530,10 +10535,10 @@
         <v>403</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10551,7 +10556,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10569,7 +10574,7 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>309</v>
@@ -10586,10 +10591,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10615,13 +10620,13 @@
         <v>364</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>367</v>
@@ -10673,7 +10678,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10691,7 +10696,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>370</v>
@@ -10708,10 +10713,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10737,13 +10742,13 @@
         <v>188</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>376</v>
@@ -10795,7 +10800,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10830,10 +10835,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10859,16 +10864,16 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10917,7 +10922,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10952,10 +10957,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10981,16 +10986,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11039,7 +11044,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11060,10 +11065,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
@@ -1982,15 +1982,15 @@
   <dimension ref="A1:AP75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.54296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2001,28 +2001,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.08984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.51953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -617,7 +617,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1014,7 +1014,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1192,7 +1192,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1221,7 +1221,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1276,7 +1276,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1306,7 +1306,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1343,7 +1343,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1418,7 +1418,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1468,7 +1468,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1501,7 +1501,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1612,7 +1612,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR 
--- a/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-bodymeasurement.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
